--- a/data/trans_camb/IQ2605_R2-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IQ2605_R2-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>8.69786103802026</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>9.955679843669651</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7.038728346570034</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.837838459358711</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>7.896678401516266</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>4.553516631472743</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>2.396258469743146</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.007601386646249</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8221635444736258</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-23.302040793748</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3.392640536126643</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-7.180721650497156</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>15.20107360218089</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>21.31761813402676</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>13.36655844301626</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.3037116085174</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>12.28346651250676</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>13.74249716594494</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.1204655522226634</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.1378863682550489</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.09559079136380801</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.05212049640121833</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1083282110791893</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.06246605037278247</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>0.03096158087122234</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.0903691483339626</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.0104283289355268</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.3223218955274794</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.04411020155595413</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1008436994827837</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.221181342687502</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.3072868603115931</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.1946439238302157</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.1568881526253187</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1747264993365789</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1921773000047269</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>1.988965395809261</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>5.706403530607885</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.226460724851632</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.839125003468701</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>3.111641665027154</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2.418620089554258</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-4.416255681928188</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.872279809067521</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.942159038994925</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-17.72997290906793</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.513561892388969</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-7.569691429769383</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>9.408418387668958</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>16.41356325171682</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>11.19777675172406</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>12.08547008577839</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>8.098174878417884</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>11.74499766810638</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.02632610699196635</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.07553041908252699</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.05758446103884609</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.03868236186020547</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.04178412038778538</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.03247800481980288</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.05686121483579745</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.1158625216733809</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.04166945619202512</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.2453523424439105</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.03174551255599701</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1010223905751289</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.1286753841935744</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.2224500102948366</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.1598241691559654</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.167560681792439</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1145533625903995</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1625097927897111</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>15.09320041147204</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>9.04571758052537</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-3.637543799162601</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>7.099060504423516</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>5.675035692196118</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>7.90537842685829</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>6.895643873964727</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.23820825724773</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-12.21490092844873</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.766610567318914</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.2164188203662948</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.05244660067665931</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>22.03209128330341</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>18.4859481823042</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.378533964933733</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>16.88087218394206</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>12.04358912504843</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>14.89644631093285</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.2209547763011409</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.13242350528713</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.04947532619066368</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.09655645498604501</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.08006650685819111</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.1115334017900608</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>0.0958812189148094</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.03161115802638505</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.1586415462362571</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.04583796650567084</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.00195238144144714</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.001046954927004217</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.3472748774193594</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.2830901160901648</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.06225830963045519</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.2453091970678485</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.1776821282326829</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.2167539073646953</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-4.673545473860397</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-12.57680776005736</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-6.541447611678642</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-13.82908657233374</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-5.516842679741929</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-13.15722187706964</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-14.58413279886322</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-30.6818080666962</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-18.39110326110574</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-29.43343847900536</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-13.33468532809814</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-25.06246843477549</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>6.029998579054741</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.015050672042609</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.761245705233923</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.9564404878695254</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.671225179746622</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-1.297869642190489</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.06137809638016702</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.1651723564409875</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.08473337304723609</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.1791323910236711</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.07199245479250901</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.1716961595910972</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.1765144009723054</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.3910278033220821</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.2242397548345945</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.3718624266316282</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.1653344143379003</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.309401916245476</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.08429029809031405</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.03668788990822485</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.05175657983301022</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.01045309566214812</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.02345795568316606</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.01645987988121752</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>6.32961446734388</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3.404478906816377</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>2.329019885960337</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-1.419186021329222</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>4.391308877245049</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1.266074097458236</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>2.458052063169638</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-3.023442644067528</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-1.475278619468474</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-8.333843856893445</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1.944772618183617</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-3.692695467735549</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>10.24648494714342</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>10.04142054228845</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>6.378468913269336</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>5.179527485909015</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>7.172962891864726</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>6.013899382034721</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.08685228356684488</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.04671481477073883</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.03149606881600284</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.01919209915722276</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.05982686554309256</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.01724889934040487</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>0.03317829103431868</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.03889932982832722</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.01940294008196766</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.1124316775403456</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0.02618576848278416</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.0491389496694536</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.1469408030232097</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.1394365912932091</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.08831945558281953</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.07092956428788441</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.09975740438469213</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.08310169183642971</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
